--- a/business_surveys/050_innovation_pipeline_readiness_survey--business_surveys.xlsx
+++ b/business_surveys/050_innovation_pipeline_readiness_survey--business_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="43" customWidth="1" min="2" max="2"/>
-    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="37" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -515,17 +515,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>business_surveys_page</t>
+          <t>has_innovation_pipeline</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Business Surveys</t>
+          <t>Does your organization have an innovation pipeline in place?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -543,12 +543,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>innovation_pipeline_readiness_survey_form</t>
+          <t>has_innovation_pipeline_score</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Innovation Pipeline Readiness Survey</t>
+          <t>Please rate your organization's innovation pipeline readiness (on a scale of 1-5)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -561,17 +561,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>what_is_the_innovation_pipeline</t>
+          <t>business_sightings</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>What is the innovation pipeline</t>
+          <t>What are the stages of the innovation pipeline that your organization is currently using?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,17 +584,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>has_innovation_pipeline</t>
+          <t>has_innovation_pipeline_readiness</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Has innovation pipeline</t>
+          <t>Do you have a clear understanding of the innovation pipeline and its benefits?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,17 +607,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>innovation_pipeline_stages</t>
+          <t>innovation_pipeline_score_1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>innovation_pipeline_stages</t>
+          <t>How do you measure the performance of your innovation pipeline?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,17 +630,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>business_sightings</t>
+          <t>has_innovation_pipeline_readiness_1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Business Sightings</t>
+          <t>How does your organization's innovation pipeline support strategic decision-making?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -658,12 +658,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>innovation_pipeline_score</t>
+          <t>business_sightings_1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Innovation Pipeline Score</t>
+          <t>What are some recent business sightings that have come from the innovation pipeline?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,17 +676,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>innovation_pipeline_description</t>
+          <t>has_innovation_pipeline_1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>innovation_pipeline_description</t>
+          <t>Does your organization have a clear understanding of the innovation pipeline and its benefits?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,7 +699,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -709,7 +709,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Innovation Pipeline Stages</t>
+          <t>Innovation Pipeline Stages 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,17 +722,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>innovation_pipeline_score_1</t>
+          <t>innovation_pipeline_stages_2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Innovation Pipeline Score</t>
+          <t>How does your organization's innovation pipeline align with your organization's goals?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -750,12 +750,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>business_sightings_1</t>
+          <t>business_sightings_2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Business Sightings</t>
+          <t>What are the challenges faced by your organization in developing and implementing its innovation pipeline?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -768,17 +768,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>innovation_pipeline_readiness</t>
+          <t>innovation_pipeline_readiness_score</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Innovation Pipeline Readiness</t>
+          <t>What is the score for your organization's innovation pipeline readiness?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -791,17 +791,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>has_innovation_pipeline_1</t>
+          <t>innovation_pipeline_stages</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Has Innovation Pipeline</t>
+          <t>Innovation Pipeline Stages</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -814,17 +814,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>innovation_pipeline_stages_1</t>
+          <t>has_innovation_pipeline_2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Innovation Pipeline Stages</t>
+          <t>Has Innovation Pipeline</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -837,17 +837,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>innovation_pipeline_description_1</t>
+          <t>innovation_pipeline_readiness</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Innovation Pipeline Description</t>
+          <t>Innovation Pipeline Readiness</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -860,113 +860,21 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>business_sightings_1</t>
+          <t>innovation_pipeline_stages_2_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Business Sightings</t>
+          <t>Innovation Pipeline Stages 2 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>innovation_pipeline_stages_2</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Innovation Pipeline Stages</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>innovation_pipeline_stages_3</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Innovation Pipeline Stages</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>innovation_pipeline_readiness_1</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Innovation Pipeline Readiness</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>innovation_pipeline_stages_4</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Innovation Pipeline Stages</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -986,7 +894,7 @@
   <dimension ref="A1:C21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="41" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1011,7 +919,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>what_is_the_innovation_pipeline_choices</t>
+          <t>has_innovation_pipeline_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1028,7 +936,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>what_is_the_innovation_pipeline_choices</t>
+          <t>has_innovation_pipeline_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1045,7 +953,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>has_innovation_pipeline_choices</t>
+          <t>has_innovation_pipeline_readiness_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1062,7 +970,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>has_innovation_pipeline_choices</t>
+          <t>has_innovation_pipeline_readiness_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1079,7 +987,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>innovation_pipeline_stages_choices</t>
+          <t>has_innovation_pipeline_readiness_1_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1096,7 +1004,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>innovation_pipeline_stages_choices</t>
+          <t>has_innovation_pipeline_readiness_1_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1113,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>innovation_pipeline_readiness_choices</t>
+          <t>has_innovation_pipeline_1_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1130,7 +1038,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>innovation_pipeline_readiness_choices</t>
+          <t>has_innovation_pipeline_1_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1147,7 +1055,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>has_innovation_pipeline_1_choices</t>
+          <t>innovation_pipeline_stages_1_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1164,7 +1072,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>has_innovation_pipeline_1_choices</t>
+          <t>innovation_pipeline_stages_1_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1181,7 +1089,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>innovation_pipeline_stages_1_choices</t>
+          <t>innovation_pipeline_stages_2_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1198,7 +1106,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>innovation_pipeline_stages_1_choices</t>
+          <t>innovation_pipeline_stages_2_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1215,7 +1123,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>innovation_pipeline_stages_2_choices</t>
+          <t>innovation_pipeline_stages_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1232,7 +1140,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>innovation_pipeline_stages_2_choices</t>
+          <t>innovation_pipeline_stages_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1249,7 +1157,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>innovation_pipeline_stages_3_choices</t>
+          <t>has_innovation_pipeline_2_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1266,7 +1174,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>innovation_pipeline_stages_3_choices</t>
+          <t>has_innovation_pipeline_2_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1283,7 +1191,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>innovation_pipeline_readiness_1_choices</t>
+          <t>innovation_pipeline_readiness_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1300,7 +1208,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>innovation_pipeline_readiness_1_choices</t>
+          <t>innovation_pipeline_readiness_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1317,7 +1225,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>innovation_pipeline_stages_4_choices</t>
+          <t>innovation_pipeline_stages_2_2_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1334,7 +1242,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>innovation_pipeline_stages_4_choices</t>
+          <t>innovation_pipeline_stages_2_2_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
